--- a/data/trans_orig/IP07A20-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A20-Estudios-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2007 (tasa de respuesta: 99,0%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2007 (tasa de respuesta: 99,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16131</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>27479</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>54,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12380</t>
+          <t>11789</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22776</t>
+          <t>22532</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>26,21%</t>
+          <t>24,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32054</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47071</t>
+          <t>47347</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,97%</t>
+          <t>32,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>14112</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>24919</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>15296</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25707</t>
+          <t>26325</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32582</t>
+          <t>32231</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47706</t>
+          <t>47773</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,07%</t>
+          <t>49,14%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1881</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8270</t>
+          <t>8331</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t>2443</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10113</t>
+          <t>9519</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14703</t>
+          <t>15485</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,93%</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1076,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5494</t>
+          <t>4359</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1106,12 +1106,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1265</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>6748</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2069</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9274</t>
+          <t>9142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>9,4%</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>681</t>
+          <t>659</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6097</t>
+          <t>6101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1199,39 +1199,39 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12,2%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3227</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
           <t>1,36%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3253</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1317</t>
+          <t>1288</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>8001</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80410</t>
+          <t>80874</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>103229</t>
+          <t>103198</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,93%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77398</t>
+          <t>77010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100600</t>
+          <t>100434</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,73%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164410</t>
+          <t>164112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>196790</t>
+          <t>198086</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,81%</t>
+          <t>45,11%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78027</t>
+          <t>77577</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>100065</t>
+          <t>100023</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97744</t>
+          <t>99331</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>123268</t>
+          <t>123160</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>41,34%</t>
+          <t>42,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>184078</t>
+          <t>183008</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>217546</t>
+          <t>215413</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,05%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11976</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24798</t>
+          <t>24410</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>25130</t>
+          <t>24810</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>42067</t>
+          <t>41540</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>40323</t>
+          <t>39978</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>61319</t>
+          <t>62459</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,22%</t>
         </is>
       </c>
     </row>
@@ -1753,12 +1753,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1466</t>
+          <t>1410</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8206</t>
+          <t>7943</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1768,12 +1768,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1788,12 +1788,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1412</t>
+          <t>1250</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8195</t>
+          <t>7975</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4093</t>
+          <t>4332</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>14023</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3007</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3163</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4101</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23927</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>37158</t>
+          <t>36599</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>35,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>14820</t>
+          <t>14764</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26567</t>
+          <t>26785</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,58%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>41509</t>
+          <t>42060</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>59530</t>
+          <t>61149</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>23787</t>
+          <t>24195</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>36825</t>
+          <t>36841</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,95%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>55,65%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23472</t>
+          <t>23815</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>36195</t>
+          <t>35642</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>59,81%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51549</t>
+          <t>50919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>69673</t>
+          <t>68827</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,99%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,4%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2236</t>
+          <t>2225</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9528</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3691</t>
+          <t>3612</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>11928</t>
+          <t>11848</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7741</t>
+          <t>7758</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>19066</t>
+          <t>18665</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,16%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3232</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2470,12 +2470,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>627</t>
+          <t>634</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5389</t>
+          <t>5929</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2485,12 +2485,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>721</t>
+          <t>663</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>6490</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>130357</t>
+          <t>128755</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>157741</t>
+          <t>158587</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,74%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>112237</t>
+          <t>113696</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>141656</t>
+          <t>142355</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>32,69%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>250338</t>
+          <t>248371</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>292281</t>
+          <t>290182</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,14%</t>
+          <t>43,82%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>124910</t>
+          <t>125097</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152441</t>
+          <t>154385</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>39,17%</t>
+          <t>39,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>145249</t>
+          <t>146029</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>175793</t>
+          <t>175146</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,31%</t>
+          <t>42,54%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,21%</t>
+          <t>51,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>278823</t>
+          <t>280819</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>320449</t>
+          <t>320318</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,4%</t>
+          <t>48,38%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19490</t>
+          <t>19229</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>36033</t>
+          <t>35707</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>34758</t>
+          <t>35781</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>55043</t>
+          <t>55196</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>59229</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>84981</t>
+          <t>85292</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -3117,12 +3117,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2757</t>
+          <t>2853</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>10782</t>
+          <t>11158</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3152,12 +3152,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>5050</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15972</t>
+          <t>15487</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3167,12 +3167,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>10142</t>
+          <t>9902</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23038</t>
+          <t>23029</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -3230,12 +3230,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1277</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>7125</t>
+          <t>7243</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3245,39 +3245,39 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>4175</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
           <t>0,4%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4162</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1956</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>9069</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -3496,7 +3496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3691,12 +3691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33982</t>
+          <t>34354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>44619</t>
+          <t>44456</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3706,12 +3706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,02%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>84,06%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>27132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37767</t>
+          <t>38014</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3741,12 +3741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64776</t>
+          <t>64919</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79748</t>
+          <t>79588</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,61%</t>
+          <t>80,44%</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5427</t>
+          <t>5257</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14963</t>
+          <t>14586</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6422</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15863</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3854,12 +3854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14173</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27360</t>
+          <t>27665</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,96%</t>
         </is>
       </c>
     </row>
@@ -3917,12 +3917,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>591</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5279</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3932,12 +3932,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3957,7 +3957,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3024</t>
+          <t>3321</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3972,7 +3972,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>648</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6394</t>
+          <t>6536</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -4035,7 +4035,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6119</t>
+          <t>4216</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4050,7 +4050,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4301</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4085,7 +4085,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4105,7 +4105,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6343</t>
+          <t>8050</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2698</t>
+          <t>2740</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4163,7 +4163,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3523</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4198,7 +4198,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4218,7 +4218,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>4559</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4233,7 +4233,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -4373,12 +4373,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>95584</t>
+          <t>95737</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>118804</t>
+          <t>118323</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4388,12 +4388,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4408,12 +4408,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>109893</t>
+          <t>108832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>135156</t>
+          <t>133546</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4423,12 +4423,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,32%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>59,43%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>212526</t>
+          <t>213114</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247900</t>
+          <t>247159</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>57,1%</t>
         </is>
       </c>
     </row>
@@ -4486,12 +4486,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>67771</t>
+          <t>66475</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90223</t>
+          <t>90191</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>32,99%</t>
+          <t>32,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>43,92%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4521,12 +4521,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69466</t>
+          <t>70728</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>93940</t>
+          <t>93697</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4536,12 +4536,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,31%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143745</t>
+          <t>143973</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178454</t>
+          <t>176746</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>33,26%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,83%</t>
         </is>
       </c>
     </row>
@@ -4599,12 +4599,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11409</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24765</t>
+          <t>24710</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4614,12 +4614,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4634,12 +4634,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10449</t>
+          <t>10553</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>22890</t>
+          <t>22698</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4649,12 +4649,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>25104</t>
+          <t>24996</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43569</t>
+          <t>43790</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,07%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4723</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4732,7 +4732,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4747,12 +4747,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>1440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7895</t>
+          <t>8289</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4767,7 +4767,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2567</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9984</t>
+          <t>10228</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4797,12 +4797,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -4830,7 +4830,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4484</t>
+          <t>4425</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4860,12 +4860,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>1270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>8688</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4875,12 +4875,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,34%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>1960</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10022</t>
+          <t>9073</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -5055,12 +5055,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>36282</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48117</t>
+          <t>49498</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5070,12 +5070,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5090,12 +5090,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>30214</t>
+          <t>29958</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>42191</t>
+          <t>42092</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>70105</t>
+          <t>69664</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87619</t>
+          <t>87297</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,41%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>71,94%</t>
         </is>
       </c>
     </row>
@@ -5168,12 +5168,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14069</t>
+          <t>12852</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>25986</t>
+          <t>25559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>40,98%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5203,12 +5203,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10954</t>
+          <t>11153</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21904</t>
+          <t>22380</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5218,12 +5218,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>27373</t>
+          <t>28069</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>43636</t>
+          <t>44986</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,56%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>37,07%</t>
         </is>
       </c>
     </row>
@@ -5286,7 +5286,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5316,12 +5316,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1353</t>
+          <t>1374</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8299</t>
+          <t>8234</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5331,12 +5331,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1534</t>
+          <t>1927</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9543</t>
+          <t>9630</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3569</t>
+          <t>3747</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5414,7 +5414,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5401</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>647</t>
+          <t>654</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>6674</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,5%</t>
         </is>
       </c>
     </row>
@@ -5737,12 +5737,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>175024</t>
+          <t>174466</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>203519</t>
+          <t>204506</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5752,12 +5752,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176634</t>
+          <t>177438</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>205886</t>
+          <t>206376</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,33%</t>
+          <t>53,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>358713</t>
+          <t>362196</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>402789</t>
+          <t>401932</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,67%</t>
+          <t>61,54%</t>
         </is>
       </c>
     </row>
@@ -5850,12 +5850,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>92578</t>
+          <t>92885</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121803</t>
+          <t>122301</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5865,12 +5865,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>95099</t>
+          <t>94866</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>124089</t>
+          <t>124125</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,71%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>196080</t>
+          <t>196475</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>236945</t>
+          <t>233712</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,78%</t>
         </is>
       </c>
     </row>
@@ -5963,12 +5963,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>13140</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>27813</t>
+          <t>28272</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13402</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>28972</t>
+          <t>28313</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30149</t>
+          <t>30710</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51007</t>
+          <t>51591</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,9%</t>
         </is>
       </c>
     </row>
@@ -6076,12 +6076,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>7287</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6091,12 +6091,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6111,12 +6111,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2982</t>
+          <t>3258</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>11449</t>
+          <t>12275</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6126,12 +6126,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5462</t>
+          <t>5256</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>15845</t>
+          <t>16144</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -6189,12 +6189,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>600</t>
+          <t>607</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5212</t>
+          <t>5211</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6224,12 +6224,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1350</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8363</t>
+          <t>8105</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6239,12 +6239,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>2684</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10685</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6455,7 +6455,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de llevarse bien con sus profesores en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6650,12 +6650,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9706</t>
+          <t>9224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18977</t>
+          <t>18694</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6665,12 +6665,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>28,99%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>59,65%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6685,12 +6685,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10870</t>
+          <t>10261</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21530</t>
+          <t>20342</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6700,12 +6700,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>28,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22725</t>
+          <t>22723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36349</t>
+          <t>36401</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6740,7 +6740,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>53,18%</t>
         </is>
       </c>
     </row>
@@ -6763,12 +6763,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9313</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18679</t>
+          <t>18575</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6778,12 +6778,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6798,12 +6798,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13271</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>23479</t>
+          <t>23521</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6813,12 +6813,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>36,22%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,2%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25929</t>
+          <t>25213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39284</t>
+          <t>39052</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>37,88%</t>
+          <t>36,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,39%</t>
+          <t>57,05%</t>
         </is>
       </c>
     </row>
@@ -6876,12 +6876,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1772</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7753</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6911,12 +6911,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>680</t>
+          <t>679</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5559</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6926,12 +6926,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3095</t>
+          <t>2717</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11151</t>
+          <t>11327</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -7029,7 +7029,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3326</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7064,7 +7064,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3421</t>
+          <t>3403</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7079,7 +7079,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,97%</t>
         </is>
       </c>
     </row>
@@ -7332,12 +7332,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>118894</t>
+          <t>119910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144550</t>
+          <t>145830</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7347,12 +7347,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7367,12 +7367,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110932</t>
+          <t>111882</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>137105</t>
+          <t>137016</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7382,12 +7382,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,21%</t>
+          <t>56,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>237990</t>
+          <t>238818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>273819</t>
+          <t>276610</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,21%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,47%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>
@@ -7445,12 +7445,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79805</t>
+          <t>78527</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104887</t>
+          <t>102994</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,0%</t>
+          <t>41,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76708</t>
+          <t>76633</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>102778</t>
+          <t>102479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7495,12 +7495,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>165182</t>
+          <t>163420</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199626</t>
+          <t>198899</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,46%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,29%</t>
         </is>
       </c>
     </row>
@@ -7558,12 +7558,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33754</t>
+          <t>33067</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7593,12 +7593,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15893</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>30824</t>
+          <t>31185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7608,12 +7608,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36831</t>
+          <t>36794</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58696</t>
+          <t>58149</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -7706,12 +7706,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1469</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8990</t>
+          <t>9391</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7721,12 +7721,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7741,12 +7741,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>1465</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8806</t>
+          <t>8694</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7761,7 +7761,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,76%</t>
         </is>
       </c>
     </row>
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>7433</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7819,12 +7819,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>722</t>
+          <t>698</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>6991</t>
+          <t>6964</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7834,12 +7834,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1410</t>
+          <t>1716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>8740</t>
+          <t>9482</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -8014,12 +8014,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>34883</t>
+          <t>34338</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>48811</t>
+          <t>48413</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8029,12 +8029,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,89%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8049,12 +8049,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42050</t>
+          <t>42587</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>56151</t>
+          <t>56402</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8064,12 +8064,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>53,87%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81193</t>
+          <t>80912</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101074</t>
+          <t>101547</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,3%</t>
+          <t>66,61%</t>
         </is>
       </c>
     </row>
@@ -8127,12 +8127,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22465</t>
+          <t>22394</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>35636</t>
+          <t>36083</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8142,12 +8142,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8162,12 +8162,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>16820</t>
+          <t>16569</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29768</t>
+          <t>29982</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8177,12 +8177,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41850</t>
+          <t>41776</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>61135</t>
+          <t>62351</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>27,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,9%</t>
         </is>
       </c>
     </row>
@@ -8240,12 +8240,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>636</t>
+          <t>699</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6287</t>
+          <t>6272</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8255,12 +8255,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8275,12 +8275,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2144</t>
+          <t>2154</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10085</t>
+          <t>9804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8290,12 +8290,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4216</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12933</t>
+          <t>13284</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,71%</t>
         </is>
       </c>
     </row>
@@ -8358,7 +8358,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4226</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8428,7 +8428,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>4360</t>
+          <t>4738</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>3,11%</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8506,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3872</t>
+          <t>4551</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8521,7 +8521,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>4056</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -8696,12 +8696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>172509</t>
+          <t>172687</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>205403</t>
+          <t>204699</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8711,12 +8711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>48,47%</t>
+          <t>48,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>173476</t>
+          <t>173853</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>203966</t>
+          <t>204992</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8746,12 +8746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>356455</t>
+          <t>354578</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>400078</t>
+          <t>402416</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>55,99%</t>
+          <t>56,32%</t>
         </is>
       </c>
     </row>
@@ -8809,12 +8809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>118373</t>
+          <t>116979</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>148833</t>
+          <t>148668</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8824,12 +8824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>41,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8844,12 +8844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>116070</t>
+          <t>116458</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>147393</t>
+          <t>146823</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8859,12 +8859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>41,1%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>243987</t>
+          <t>244320</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>286054</t>
+          <t>288686</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>40,4%</t>
         </is>
       </c>
     </row>
@@ -8922,12 +8922,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23636</t>
+          <t>22959</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>40761</t>
+          <t>39371</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8937,12 +8937,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8957,12 +8957,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>22118</t>
+          <t>21012</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>40641</t>
+          <t>38879</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8972,12 +8972,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49672</t>
+          <t>49835</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>74192</t>
+          <t>72745</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4670</t>
+          <t>4887</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9055,7 +9055,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2109</t>
+          <t>2167</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>9813</t>
+          <t>10337</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9085,12 +9085,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3021</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>11450</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -9153,7 +9153,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5894</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9168,7 +9168,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9183,12 +9183,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1380</t>
+          <t>1366</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>7684</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9203,7 +9203,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2056</t>
+          <t>2250</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10196</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP07A20-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP07A20-Estudios-trans_orig.xlsx
@@ -537,13 +537,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2007 (tasa de respuesta: 99,0%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el/la adulto/a [KIDSCREEN 20] en 2007 (tasa de respuesta: 99,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -722,72 +722,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>17382</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>12361</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>22521</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>36,8%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>26,17%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>47,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>33</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>21943</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>16555</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>27479</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>16452</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>28114</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>43,89%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>33,12%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>54,97%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>17382</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>11789</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>22532</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>36,8%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>47,71%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>32084</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47347</t>
+          <t>46635</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,7%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>48,7%</t>
+          <t>47,97%</t>
         </is>
       </c>
     </row>
@@ -835,72 +835,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20613</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15731</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>26203</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>33,31%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>55,48%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>19586</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14112</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>24919</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>14067</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>25193</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>39,18%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>49,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20613</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>15296</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>26325</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>43,64%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>50,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32231</t>
+          <t>32759</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>47773</t>
+          <t>47866</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,23%</t>
         </is>
       </c>
     </row>
@@ -948,72 +948,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5290</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2590</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9861</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,2%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,48%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>20,88%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4416</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1913</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>8331</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1915</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>8949</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>8,83%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>16,67%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5290</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2443</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>9519</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>5,17%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5385</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15485</t>
+          <t>15886</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>16,34%</t>
         </is>
       </c>
     </row>
@@ -1061,72 +1061,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3301</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1249</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6740</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6,99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,65%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>14,27%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>1378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4359</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4806</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,76%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>3301</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6748</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>6,99%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>2,66%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,29%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1141,12 +1141,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1156,12 +1156,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>8,96%</t>
         </is>
       </c>
     </row>
@@ -1174,72 +1174,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3588</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>7,6%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>2668</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>659</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6101</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>683</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>6558</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>5,34%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>12,2%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3227</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1288</t>
+          <t>1293</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>7337</t>
+          <t>7143</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1269,12 +1269,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,35%</t>
         </is>
       </c>
     </row>
@@ -1287,57 +1287,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>47230</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>49990</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>49990</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>49990</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>47230</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1404,72 +1404,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>88799</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>77308</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>100687</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>37,55%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>32,69%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>42,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>91559</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>80874</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>103198</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>80254</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>101297</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>45,17%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>39,9%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>50,91%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>134</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>88799</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>77010</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>100434</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>37,55%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>39,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>49,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>164112</t>
+          <t>165101</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>198086</t>
+          <t>195743</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,37%</t>
+          <t>37,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -1517,72 +1517,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>110582</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>98959</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>122935</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>46,76%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>41,85%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>51,99%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>89168</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77577</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100023</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>78707</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>100550</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>43,99%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>38,27%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>49,35%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>110582</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>99331</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>123160</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>46,76%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,01%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>52,08%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183008</t>
+          <t>183102</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>215413</t>
+          <t>215171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,67%</t>
+          <t>41,69%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>49,05%</t>
+          <t>49,0%</t>
         </is>
       </c>
     </row>
@@ -1630,72 +1630,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>32436</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>23780</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>41430</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>13,72%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>10,06%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>17,52%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17490</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>12280</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24410</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>12129</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>25055</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,63%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,04%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>32436</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>24810</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>41540</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>13,72%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>39978</t>
+          <t>40701</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>62459</t>
+          <t>60680</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>13,82%</t>
         </is>
       </c>
     </row>
@@ -1748,67 +1748,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3931</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1277</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7884</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,66%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,54%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>3877</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1410</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7943</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1387</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8230</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>1,91%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,92%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3931</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1250</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7975</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4332</t>
+          <t>3956</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14023</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -1861,102 +1861,102 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>3381</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>2980</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>1,74%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>1,47%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3995</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>1,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1317</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,3%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,99%</t>
         </is>
       </c>
     </row>
@@ -1969,57 +1969,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>357</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>236467</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>236467</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>236467</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>303</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>202692</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>202692</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>202692</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>357</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>236467</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>236467</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>236467</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2086,72 +2086,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>20525</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>14832</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>26050</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>34,44%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>24,89%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>43,71%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>30365</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>23458</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>36599</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>23984</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>36888</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>45,89%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>35,45%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>55,31%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>20525</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>14764</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>26785</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>34,44%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>36,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>55,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>42060</t>
+          <t>41616</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>61149</t>
+          <t>60962</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>33,44%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>48,47%</t>
         </is>
       </c>
     </row>
@@ -2199,72 +2199,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>29866</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>23142</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>35996</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>50,12%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>38,83%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>60,4%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>30054</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>24195</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>36841</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>23709</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>37171</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>45,42%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>36,56%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>55,68%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>29866</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>23815</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>35642</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>50,12%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>35,83%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>56,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>50919</t>
+          <t>50487</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>68827</t>
+          <t>70100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>40,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>55,74%</t>
         </is>
       </c>
     </row>
@@ -2312,72 +2312,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>7029</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>3446</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>12294</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>11,8%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,78%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>20,63%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>5099</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>2225</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>10303</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2173</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>9730</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,71%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>3,36%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>15,57%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>7029</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>3612</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>11848</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>11,8%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7758</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18665</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,04%</t>
         </is>
       </c>
     </row>
@@ -2425,72 +2425,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>2172</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>636</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>5897</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3,64%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,9%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>654</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3232</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>3277</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>4,88%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2172</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>634</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5929</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>3,64%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2505,12 +2505,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>727</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6490</t>
+          <t>7084</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2520,12 +2520,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -2651,57 +2651,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>59592</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>59592</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>59592</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>66171</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>66171</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>66171</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>59592</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>59592</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>59592</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2768,72 +2768,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>126706</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>112293</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>139990</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>36,91%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>32,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>40,78%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>214</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>143867</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>128755</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>158587</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>129108</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>157774</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>45,12%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>40,38%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>49,74%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>190</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>126706</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>113696</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>142355</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>36,91%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>248371</t>
+          <t>248353</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>290182</t>
+          <t>291460</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,82%</t>
+          <t>44,02%</t>
         </is>
       </c>
     </row>
@@ -2881,72 +2881,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>161061</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>146878</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>175755</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>46,92%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>42,79%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>51,2%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>205</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>138807</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>125097</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>154385</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>125415</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>153784</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>43,53%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>39,23%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>48,42%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>161061</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>146029</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>175146</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>46,92%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>42,54%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>48,23%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>280819</t>
+          <t>280219</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>320318</t>
+          <t>322118</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>42,41%</t>
+          <t>42,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,65%</t>
         </is>
       </c>
     </row>
@@ -2994,72 +2994,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>44755</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>35560</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>55827</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>13,04%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>10,36%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>16,26%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>27004</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>19229</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>35707</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>19195</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>36029</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>8,47%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,03%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>44755</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>35781</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>55196</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>13,04%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>60014</t>
+          <t>60012</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>85292</t>
+          <t>84487</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,76%</t>
         </is>
       </c>
     </row>
@@ -3107,72 +3107,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>9403</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>15146</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>1,53%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>5909</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>2853</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>11158</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>2679</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>10909</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>1,85%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>3,5%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>9403</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>5050</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>15487</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>9902</t>
+          <t>10288</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23029</t>
+          <t>22310</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -3220,74 +3220,74 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>1363</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,35%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>3266</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>1258</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>7243</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>1278</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>7236</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>1,02%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>2,27%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>1363</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>4175</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>7</t>
@@ -3300,12 +3300,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1956</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9069</t>
+          <t>9869</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,49%</t>
         </is>
       </c>
     </row>
@@ -3333,57 +3333,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>516</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>343289</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>343289</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>343289</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>473</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>318853</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>318853</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>318853</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>516</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>343289</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>343289</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>343289</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3496,13 +3496,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2012 (tasa de respuesta: 97,91%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el/la adulto/a [KIDSCREEN 20] en 2012 (tasa de respuesta: 97,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3513,7 +3513,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3681,72 +3681,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>33201</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>27777</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37648</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>72,41%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>82,11%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>39939</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>34354</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>44456</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>33939</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>44506</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>75,24%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>64,72%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>83,75%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>33201</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>27132</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>38014</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>72,41%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>83,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64919</t>
+          <t>65794</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>79588</t>
+          <t>79682</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3776,12 +3776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,54%</t>
         </is>
       </c>
     </row>
@@ -3794,72 +3794,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>10529</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6584</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>15773</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>22,96%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>14,36%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>34,4%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>9504</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5257</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>14586</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>14578</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>17,9%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>9,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,48%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>10529</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6422</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>16151</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>22,96%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,01%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>35,22%</t>
+          <t>27,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>13885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>27665</t>
+          <t>27164</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3889,12 +3889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>14,48%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,46%</t>
         </is>
       </c>
     </row>
@@ -3907,72 +3907,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3356</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,32%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1926</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5279</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5296</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,63%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="O6" s="2" t="inlineStr">
         <is>
           <t>1,12%</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>9,95%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>3321</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3987,12 +3987,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>658</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6015</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4002,12 +4002,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,08%</t>
         </is>
       </c>
     </row>
@@ -4025,102 +4025,102 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4561</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,9%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,95%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1058</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4216</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5221</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>1,99%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>7,94%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>869</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>9,84%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>1927</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4808</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,9%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>6129</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>10,49%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>1927</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>8050</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -4138,102 +4138,102 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2737</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>5,97%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>656</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2740</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3412</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>1,24%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>5,16%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>6,43%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>1263</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3523</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>4486</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>1,28%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>7,68%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>1263</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4559</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>1,28%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -4246,57 +4246,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>45853</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>53083</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>45853</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4363,72 +4363,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>121919</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>109712</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>134111</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>53,61%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>48,24%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>58,97%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>107366</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>95737</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>118323</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>96067</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>119692</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>52,27%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>46,61%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>57,6%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>177</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>121919</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>108832</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>133546</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>53,61%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,86%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4443,12 +4443,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>213114</t>
+          <t>211996</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>247159</t>
+          <t>245756</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4458,12 +4458,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>48,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,1%</t>
+          <t>56,78%</t>
         </is>
       </c>
     </row>
@@ -4476,72 +4476,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>82220</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>70340</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>94195</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,15%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>30,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>41,42%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>78219</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>66475</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>90191</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>66718</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>89903</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>38,08%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>43,91%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>82220</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>70728</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>93697</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,15%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4556,12 +4556,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>143973</t>
+          <t>144674</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>176746</t>
+          <t>177103</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,26%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,83%</t>
+          <t>40,92%</t>
         </is>
       </c>
     </row>
@@ -4589,72 +4589,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>16054</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>10650</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>23249</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,06%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,22%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>24</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>17193</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>11409</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>24710</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>11197</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>25681</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>8,37%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>5,55%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>12,03%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>16054</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>10553</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>22698</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4669,12 +4669,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>24996</t>
+          <t>24928</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>43790</t>
+          <t>43552</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4684,12 +4684,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -4702,72 +4702,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3893</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1752</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8915</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,71%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,92%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>1353</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4697</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,66%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3893</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1440</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>8289</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4782,12 +4782,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2567</t>
+          <t>2543</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10228</t>
+          <t>9808</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,27%</t>
         </is>
       </c>
     </row>
@@ -4815,72 +4815,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3331</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1207</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>7587</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,53%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1287</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4425</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4966</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,63%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>3331</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>1270</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>8688</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,56%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4895,12 +4895,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1864</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9073</t>
+          <t>8652</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4910,12 +4910,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,0%</t>
         </is>
       </c>
     </row>
@@ -4928,57 +4928,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>227419</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>227419</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>227419</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>294</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>205418</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>205418</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>205418</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>332</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>227419</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>227419</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>227419</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5045,72 +5045,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>36289</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>30167</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42019</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>62,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>52,07%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72,53%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>42720</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>36159</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>49498</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>36074</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>49002</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>67,36%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>57,02%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>78,05%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>36289</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>29958</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>42092</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>62,64%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,66%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5125,12 +5125,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>69664</t>
+          <t>70577</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>87297</t>
+          <t>86724</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5140,12 +5140,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>57,41%</t>
+          <t>58,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,47%</t>
         </is>
       </c>
     </row>
@@ -5158,72 +5158,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>16341</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>11097</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>21723</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,21%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19,15%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>37,5%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>19162</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>12852</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>25559</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>12963</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>25487</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>30,22%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>20,27%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>40,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>16341</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>11153</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>22380</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,21%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5238,12 +5238,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>28069</t>
+          <t>28315</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>44986</t>
+          <t>43350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5253,12 +5253,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>35,72%</t>
         </is>
       </c>
     </row>
@@ -5271,72 +5271,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>3715</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>1378</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>8293</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>14,31%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>3842</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3690</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,06%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>3715</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>8234</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,41%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5351,12 +5351,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1927</t>
+          <t>1719</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9141</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5366,12 +5366,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,53%</t>
         </is>
       </c>
     </row>
@@ -5384,72 +5384,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>1588</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>6165</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>10,64%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>3747</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4092</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,21%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,91%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>1588</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>5225</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5464,12 +5464,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>654</t>
+          <t>645</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6674</t>
+          <t>6179</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5479,12 +5479,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,09%</t>
         </is>
       </c>
     </row>
@@ -5610,57 +5610,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>57933</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>63418</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>57933</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5727,72 +5727,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>277</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>191408</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>175847</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>206235</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>57,79%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>53,09%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>62,27%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>270</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>190024</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>174466</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>204506</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>174054</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>204083</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>59,03%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>54,2%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>63,53%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>277</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>191408</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>177438</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>206376</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>57,79%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,57%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>362196</t>
+          <t>360327</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>401932</t>
+          <t>402244</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5822,12 +5822,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>61,54%</t>
+          <t>61,59%</t>
         </is>
       </c>
     </row>
@@ -5840,72 +5840,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>109090</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>95671</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>123921</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>32,94%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>28,89%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>37,42%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>106885</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>92885</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>122301</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>93821</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>121971</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>33,2%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>28,85%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>37,99%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>109090</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>94866</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>124125</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>32,94%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>196475</t>
+          <t>196594</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>233712</t>
+          <t>237320</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>36,34%</t>
         </is>
       </c>
     </row>
@@ -5953,72 +5953,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>20417</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>13238</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>27987</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>8,45%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>19887</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>13759</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>28272</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>13557</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>28557</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>6,18%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>4,27%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>8,78%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>20417</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>13402</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>28313</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>30710</t>
+          <t>30594</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>51591</t>
+          <t>50777</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,77%</t>
         </is>
       </c>
     </row>
@@ -6066,72 +6066,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>6351</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>3083</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>11438</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,92%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,93%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>3179</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>7634</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>1056</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>7596</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,99%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,33%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>6351</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>3258</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>12275</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,92%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6146,12 +6146,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5256</t>
+          <t>5022</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>16144</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6161,12 +6161,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,4%</t>
         </is>
       </c>
     </row>
@@ -6179,72 +6179,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3938</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>8587</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,59%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1943</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5211</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>608</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5416</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,6%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3938</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1304</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>8105</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,19%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6259,12 +6259,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2684</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10708</t>
+          <t>11065</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6274,12 +6274,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -6292,57 +6292,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>482</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>331204</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>331204</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>331204</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>457</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>321919</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>321919</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>321919</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>482</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>331204</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>331204</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>331204</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6455,13 +6455,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el adulto en 2016 (tasa de respuesta: 98,52%)</t>
+          <t>Menores según la frecuencia de llevarse bien con el profesorado, percibida por el/la adulto/a [KIDSCREEN 20] en 2016 (tasa de respuesta: 98,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6472,7 +6472,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6640,72 +6640,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>15325</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>10559</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>20550</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>28,82%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56,09%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>13935</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>9224</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>18694</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>9680</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>18620</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>43,8%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>28,99%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>58,76%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>15325</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10261</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>20342</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>41,83%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,52%</t>
+          <t>58,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6720,12 +6720,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>22723</t>
+          <t>22674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36401</t>
+          <t>36472</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6735,12 +6735,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,28%</t>
         </is>
       </c>
     </row>
@@ -6753,72 +6753,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>18543</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>13150</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23570</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>35,89%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>64,33%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>13921</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>9035</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>18575</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>9481</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>18356</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>43,76%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>28,4%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>58,39%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>18543</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>13623</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>23521</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>50,61%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>29,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,2%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6833,12 +6833,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>25213</t>
+          <t>25635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>39052</t>
+          <t>39272</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6848,12 +6848,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,05%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -6866,72 +6866,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>675</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>14,88%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>3958</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>1772</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7706</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>1381</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>7646</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>12,44%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,57%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>24,22%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>2099</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>5197</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6946,12 +6946,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2717</t>
+          <t>2687</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11327</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6961,12 +6961,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -6979,107 +6979,107 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>671</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3283</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,96%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="R7" s="2" t="inlineStr">
         <is>
           <t>671</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="S7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>3452</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,83%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>3768</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>0,98%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>9,42%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>671</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -7205,57 +7205,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>36638</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>31814</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>36638</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7322,72 +7322,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>124162</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>110230</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>137446</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>50,91%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>45,19%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>56,35%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>189</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>132703</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>119910</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>145830</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>120143</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>145267</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>53,14%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>48,02%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>58,4%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>124162</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>111882</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>137016</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>50,91%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,87%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7402,12 +7402,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238818</t>
+          <t>238261</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>276610</t>
+          <t>275499</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7417,12 +7417,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>55,81%</t>
         </is>
       </c>
     </row>
@@ -7435,72 +7435,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>90079</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>77065</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>102592</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>36,93%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,6%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>42,06%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>132</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>90905</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>78527</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>102994</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>79473</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>104007</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>36,4%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>31,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>41,24%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>90079</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>76633</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>102479</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>36,93%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,65%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7515,12 +7515,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>163420</t>
+          <t>164417</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>198899</t>
+          <t>199655</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7530,12 +7530,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>33,11%</t>
+          <t>33,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>40,29%</t>
+          <t>40,45%</t>
         </is>
       </c>
     </row>
@@ -7548,72 +7548,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>22480</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>15571</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>30527</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>9,22%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>6,38%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,52%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>24487</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>18286</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>33067</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>17171</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>33249</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>9,81%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>13,24%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>22480</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>15779</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>31185</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>9,22%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7628,12 +7628,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>36794</t>
+          <t>36412</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58149</t>
+          <t>58213</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7643,12 +7643,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -7661,92 +7661,92 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4407</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1487</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8620</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>3,53%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
+      <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K13" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>4407</t>
         </is>
       </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>2061</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9391</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>4407</t>
-        </is>
-      </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>2094</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>8694</t>
+          <t>9459</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -7774,72 +7774,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2773</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>699</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>6201</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>2,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>1621</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>6225</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>6068</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>0,65%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>2773</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>698</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>6964</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7854,12 +7854,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1716</t>
+          <t>1680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>9482</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,82%</t>
         </is>
       </c>
     </row>
@@ -7887,57 +7887,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>243901</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>243901</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>243901</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>359</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>249716</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>249716</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>249716</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>333</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>243901</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>243901</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>243901</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8004,72 +8004,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>49929</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>42692</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>56443</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>63,96%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>54,69%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>72,31%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>58</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>41498</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>34338</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>48413</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>34415</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>48506</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>55,78%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>46,15%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>65,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>49929</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>42587</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>56402</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>63,96%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,56%</t>
+          <t>46,26%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>72,25%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8084,12 +8084,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>80912</t>
+          <t>80419</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>101547</t>
+          <t>101732</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>53,07%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>66,73%</t>
         </is>
       </c>
     </row>
@@ -8117,72 +8117,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>22445</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>16063</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>30298</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>28,75%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>20,58%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>38,81%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>28913</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>22394</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>36083</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>22447</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>36544</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,86%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>30,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>48,5%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>22445</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>16569</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>29982</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>28,75%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>30,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8197,12 +8197,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41776</t>
+          <t>41613</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>62351</t>
+          <t>61306</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,9%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -8230,72 +8230,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>4988</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>9707</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2,68%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,44%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>2625</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6272</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6336</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>3,53%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,94%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>4988</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>2154</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>9804</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,39%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8310,12 +8310,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4149</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13284</t>
+          <t>13775</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8325,12 +8325,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -8343,107 +8343,107 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>1361</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>4226</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>4389</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>1,83%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,68%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>5,9%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5365</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>4738</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,52%</t>
         </is>
       </c>
     </row>
@@ -8456,107 +8456,107 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>3463</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,9%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>700</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>4551</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>3560</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>5,83%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>3877</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -8569,57 +8569,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>78061</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>104</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>74398</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>78061</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8686,72 +8686,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>189416</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>173544</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>205271</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>52,82%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>48,39%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>57,24%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>188136</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>172687</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>204699</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>172613</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>203353</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
         <is>
           <t>52,86%</t>
         </is>
       </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>48,52%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>57,51%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>261</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>189416</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>173853</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>204992</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>52,82%</t>
-        </is>
-      </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>354578</t>
+          <t>355292</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>402416</t>
+          <t>399331</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8781,12 +8781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,62%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>55,89%</t>
         </is>
       </c>
     </row>
@@ -8799,72 +8799,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>131066</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>116917</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>147427</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>36,55%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>32,6%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>41,11%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
         <is>
           <t>133739</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>116979</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>148668</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>118331</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>148872</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>37,57%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>32,87%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>41,77%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>179</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>131066</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>116458</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>146823</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>36,55%</t>
-        </is>
-      </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>32,48%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>40,94%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>244320</t>
+          <t>244565</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>288686</t>
+          <t>286233</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8894,12 +8894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,19%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,06%</t>
         </is>
       </c>
     </row>
@@ -8912,72 +8912,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>29567</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>22261</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>39555</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>8,25%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>31070</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>22959</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>39371</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>23231</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>40715</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>8,73%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>29567</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>21012</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>38879</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8992,12 +8992,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>49835</t>
+          <t>49037</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>72745</t>
+          <t>72610</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9007,12 +9007,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,16%</t>
         </is>
       </c>
     </row>
@@ -9025,72 +9025,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>5078</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>2217</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>10145</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>2,83%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>1361</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>4887</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5395</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>5078</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>2167</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>10337</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9105,12 +9105,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>2941</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>12160</t>
+          <t>12280</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9120,12 +9120,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -9138,72 +9138,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>3473</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>7000</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>0,38%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>1621</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5838</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5884</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>3473</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>1366</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>7684</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>0,97%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9218,12 +9218,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2250</t>
+          <t>2179</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>10758</t>
+          <t>9875</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -9251,57 +9251,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>492</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>358600</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>358600</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>358600</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="K27" s="2" t="inlineStr">
         <is>
           <t>355928</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>355928</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="M27" s="2" t="inlineStr">
         <is>
           <t>355928</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>492</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>358600</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
-        <is>
-          <t>358600</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr">
-        <is>
-          <t>358600</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
